--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>72240008163000</v>
+        <v>8163000</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>30346</v>
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>79010008612000</v>
+        <v>8612000</v>
       </c>
       <c r="I281" s="5" t="n">
         <v>24606</v>

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>8163000</v>
+        <v>72240008163000</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>30346</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2365,34 +2365,34 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>13973500</v>
+        <v>14709000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>27292</v>
+        <v>28729</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>13973500</v>
+        <v>13238100</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>27292</v>
+        <v>25856</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9127,23 +9127,23 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>6662000</v>
+        <v>5995800</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>24403</v>
+        <v>21963</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="5" t="n">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9631,34 +9631,34 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>9208000</v>
+        <v>8747600</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>26460</v>
+        <v>25137</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>8287200</v>
+        <v>8747600</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>23814</v>
+        <v>25137</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15862,7 +15862,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17509,23 +17509,23 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
-        <v>13089000</v>
+        <v>11780100</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>25564</v>
+        <v>23008</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K268" s="5" t="n">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>8612000</v>
+        <v>79010008612000</v>
       </c>
       <c r="I281" s="5" t="n">
         <v>24606</v>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -19042,7 +19042,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21928,7 +21928,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23068,7 +23068,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23386,7 +23386,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23642,7 +23642,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24332,7 +24332,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24898,7 +24898,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25456,7 +25456,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25890,7 +25890,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -26014,7 +26014,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27381,12 +27381,12 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1397万
-$27,292/呎
-(26年-07月-21日)</t>
+$1471万
+$28,729/呎
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -27402,7 +27402,7 @@
           <t>C | 350呎 (2房)
 $911万
 $26,030/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>D | 350呎 (2房)
 $913万
 $26,084/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -27418,7 +27418,7 @@
           <t>E | 348呎 (2房)
 $862万
 $24,778/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -27426,7 +27426,7 @@
           <t>F | 348呎 (2房)
 $901万
 $25,893/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -27434,7 +27434,7 @@
           <t>G | 348呎 (2房)
 $853万
 $24,517/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -27442,7 +27442,7 @@
           <t>H | 348呎 (2房)
 $810万
 $23,276/呎
-(26年-05月-08日)</t>
+(26年-05月-09日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -27466,7 +27466,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,300/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="M6" s="23" t="inlineStr">
@@ -27474,7 +27474,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,605/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -27490,7 +27490,7 @@
           <t>P | 273呎 (1房)
 $567万
 $20,763/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="P6" s="23" t="inlineStr">
@@ -27498,7 +27498,7 @@
           <t>Q | 273呎 (1房)
 $561万
 $20,565/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -27513,7 +27513,7 @@
           <t>A | 512呎 (3房)
 $1196万
 $23,368/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -27521,7 +27521,7 @@
           <t>B | 397呎 (3房)
 $906万
 $22,831/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -27529,7 +27529,7 @@
           <t>C | 350呎 (2房)
 $803万
 $22,929/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -27537,7 +27537,7 @@
           <t>D | 350呎 (2房)
 $804万
 $22,978/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -27545,7 +27545,7 @@
           <t>E | 348呎 (2房)
 $802万
 $23,038/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -27593,7 +27593,7 @@
           <t>L | 270呎 (1房)
 $525万
 $19,430/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M7" s="23" t="inlineStr">
@@ -27601,7 +27601,7 @@
           <t>M | 265呎 (1房)
 $552万
 $20,814/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -27617,7 +27617,7 @@
           <t>P | 273呎 (1房)
 $542万
 $19,840/呎
-(26年-05月-08日)</t>
+(26年-05月-09日)</t>
         </is>
       </c>
       <c r="P7" s="23" t="inlineStr">
@@ -27625,7 +27625,7 @@
           <t>Q | 273呎 (1房)
 $536万
 $19,642/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -27640,7 +27640,7 @@
           <t>A | 512呎 (3房)
 $1190万
 $23,237/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -27648,7 +27648,7 @@
           <t>B | 397呎 (3房)
 $901万
 $22,702/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>C | 350呎 (2房)
 $811万
 $23,181/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>D | 350呎 (2房)
 $844万
 $24,119/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>F | 348呎 (2房)
 $858万
 $24,644/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -27720,7 +27720,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,373/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M8" s="23" t="inlineStr">
@@ -27728,7 +27728,7 @@
           <t>M | 265呎 (1房)
 $521万
 $19,661/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -27744,7 +27744,7 @@
           <t>P | 273呎 (1房)
 $543万
 $19,893/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
@@ -27752,7 +27752,7 @@
           <t>Q | 273呎 (1房)
 $535万
 $19,586/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -27767,7 +27767,7 @@
           <t>A | 512呎 (3房)
 $1218万
 $23,783/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>B | 397呎 (3房)
 $946万
 $23,829/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,672/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -27791,7 +27791,7 @@
           <t>D | 350呎 (2房)
 $795万
 $22,724/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>E | 348呎 (2房)
 $837万
 $24,045/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -27847,7 +27847,7 @@
           <t>L | 270呎 (1房)
 $522万
 $19,320/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M9" s="23" t="inlineStr">
@@ -27855,7 +27855,7 @@
           <t>M | 265呎 (1房)
 $520万
 $19,606/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -27871,7 +27871,7 @@
           <t>P | 273呎 (1房)
 $538万
 $19,724/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
@@ -27879,7 +27879,7 @@
           <t>Q | 273呎 (1房)
 $533万
 $19,526/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
           <t>A | 512呎 (3房)
 $1211万
 $23,648/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -27902,7 +27902,7 @@
           <t>B | 397呎 (3房)
 $954万
 $24,029/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -27910,7 +27910,7 @@
           <t>C | 350呎 (2房)
 $833万
 $23,796/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -27918,7 +27918,7 @@
           <t>D | 350呎 (2房)
 $835万
 $23,850/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -27926,7 +27926,7 @@
           <t>E | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -27942,7 +27942,7 @@
           <t>G | 348呎 (2房)
 $761万
 $21,861/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -27950,7 +27950,7 @@
           <t>H | 348呎 (2房)
 $805万
 $23,128/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -27974,7 +27974,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,374/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
@@ -27982,7 +27982,7 @@
           <t>M | 265呎 (1房)
 $547万
 $20,638/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -27998,7 +27998,7 @@
           <t>P | 273呎 (1房)
 $537万
 $19,668/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
@@ -28006,7 +28006,7 @@
           <t>Q | 273呎 (1房)
 $534万
 $19,578/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28021,7 @@
           <t>A | 512呎 (3房)
 $1161万
 $22,671/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28037,7 +28037,7 @@
           <t>C | 350呎 (2房)
 $812万
 $23,207/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -28045,7 +28045,7 @@
           <t>D | 350呎 (2房)
 $828万
 $23,646/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>E | 348呎 (2房)
 $816万
 $23,444/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -28069,7 +28069,7 @@
           <t>G | 348呎 (2房)
 $761万
 $21,861/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -28077,7 +28077,7 @@
           <t>H | 348呎 (2房)
 $813万
 $23,371/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -28085,7 +28085,7 @@
           <t>J | 464呎 (3房)
 $1133万
 $24,417/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -28101,7 +28101,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,374/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M11" s="23" t="inlineStr">
@@ -28109,7 +28109,7 @@
           <t>M | 265呎 (1房)
 $518万
 $19,552/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -28133,7 +28133,7 @@
           <t>Q | 273呎 (1房)
 $601万
 $22,002/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28148,7 @@
           <t>A | 512呎 (3房)
 $1148万
 $22,412/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>B | 397呎 (3房)
 $933万
 $23,491/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>C | 350呎 (2房)
 $807万
 $23,070/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -28172,7 +28172,7 @@
           <t>D | 350呎 (2房)
 $805万
 $22,994/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -28180,7 +28180,7 @@
           <t>E | 348呎 (2房)
 $802万
 $23,051/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -28196,7 +28196,7 @@
           <t>G | 348呎 (2房)
 $752万
 $21,613/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -28204,7 +28204,7 @@
           <t>H | 348呎 (2房)
 $804万
 $23,106/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -28212,7 +28212,7 @@
           <t>J | 464呎 (3房)
 $1061万
 $22,872/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -28228,7 +28228,7 @@
           <t>L | 270呎 (1房)
 $517万
 $19,157/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -28236,7 +28236,7 @@
           <t>M | 265呎 (1房)
 $544万
 $20,520/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -28260,7 +28260,7 @@
           <t>Q | 273呎 (1房)
 $597万
 $21,870/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -28275,7 +28275,7 @@
           <t>A | 512呎 (3房)
 $1141万
 $22,282/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>B | 397呎 (3房)
 $927万
 $23,355/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>C | 350呎 (2房)
 $798万
 $22,811/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -28299,7 +28299,7 @@
           <t>D | 350呎 (2房)
 $800万
 $22,860/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -28307,7 +28307,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,916/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -28315,7 +28315,7 @@
           <t>F | 348呎 (2房)
 $833万
 $23,951/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -28323,7 +28323,7 @@
           <t>G | 348呎 (2房)
 $824万
 $23,677/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -28331,7 +28331,7 @@
           <t>H | 348呎 (2房)
 $799万
 $22,974/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -28339,7 +28339,7 @@
           <t>J | 464呎 (3房)
 $1055万
 $22,742/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -28355,7 +28355,7 @@
           <t>L | 270呎 (1房)
 $583万
 $21,583/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -28363,7 +28363,7 @@
           <t>M | 265呎 (1房)
 $580万
 $21,906/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -28387,7 +28387,7 @@
           <t>Q | 273呎 (1房)
 $595万
 $21,808/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -28402,7 +28402,7 @@
           <t>A | 512呎 (3房)
 $1134万
 $22,152/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -28410,7 +28410,7 @@
           <t>B | 397呎 (3房)
 $973万
 $24,509/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,677/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,729/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -28434,15 +28434,15 @@
           <t>E | 348呎 (2房)
 $797万
 $22,911/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$921万
-$26,460/呎
-(在售)</t>
+$875万
+$25,137/呎
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -28450,7 +28450,7 @@
           <t>G | 348呎 (2房)
 $819万
 $23,540/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -28458,7 +28458,7 @@
           <t>H | 348呎 (2房)
 $821万
 $23,594/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -28466,7 +28466,7 @@
           <t>J | 464呎 (3房)
 $1107万
 $23,867/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -28482,7 +28482,7 @@
           <t>L | 270呎 (1房)
 $581万
 $21,523/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -28490,7 +28490,7 @@
           <t>M | 265呎 (1房)
 $579万
 $21,841/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -28501,12 +28501,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="O14" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
-$666万
-$24,403/呎
-(在售)</t>
+$600万
+$21,963/呎
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="P14" s="23" t="inlineStr">
@@ -28514,7 +28514,7 @@
           <t>Q | 273呎 (1房)
 $594万
 $21,742/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
           <t>A | 512呎 (3房)
 $1126万
 $21,987/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -28537,7 +28537,7 @@
           <t>B | 397呎 (3房)
 $891万
 $22,443/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -28545,7 +28545,7 @@
           <t>C | 350呎 (2房)
 $789万
 $22,546/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -28553,7 +28553,7 @@
           <t>D | 350呎 (2房)
 $835万
 $23,853/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -28561,7 +28561,7 @@
           <t>E | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -28569,7 +28569,7 @@
           <t>F | 348呎 (2房)
 $824万
 $23,674/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -28577,7 +28577,7 @@
           <t>G | 348呎 (2房)
 $814万
 $23,403/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -28593,7 +28593,7 @@
           <t>J | 464呎 (3房)
 $1043万
 $22,481/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -28609,7 +28609,7 @@
           <t>L | 270呎 (1房)
 $580万
 $21,463/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="M15" s="23" t="inlineStr">
@@ -28617,7 +28617,7 @@
           <t>M | 265呎 (1房)
 $577万
 $21,780/呎
-(26年-05月-30日)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -28633,7 +28633,7 @@
           <t>P | 273呎 (1房)
 $529万
 $19,381/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="P15" s="23" t="inlineStr">
@@ -28641,7 +28641,7 @@
           <t>Q | 273呎 (1房)
 $524万
 $19,184/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28656,7 @@
           <t>A | 512呎 (3房)
 $1136万
 $22,184/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -28664,7 +28664,7 @@
           <t>B | 397呎 (3房)
 $860万
 $21,675/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -28672,7 +28672,7 @@
           <t>C | 350呎 (2房)
 $793万
 $22,645/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -28680,7 +28680,7 @@
           <t>D | 350呎 (2房)
 $794万
 $22,697/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -28688,7 +28688,7 @@
           <t>E | 348呎 (2房)
 $792万
 $22,751/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -28704,7 +28704,7 @@
           <t>G | 348呎 (2房)
 $810万
 $23,266/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -28712,7 +28712,7 @@
           <t>H | 348呎 (2房)
 $812万
 $23,320/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -28720,7 +28720,7 @@
           <t>J | 464呎 (3房)
 $1084万
 $23,352/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -28728,7 +28728,7 @@
           <t>K | 395呎 (3房)
 $845万
 $21,384/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
@@ -28736,7 +28736,7 @@
           <t>L | 270呎 (1房)
 $511万
 $18,937/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
@@ -28744,7 +28744,7 @@
           <t>M | 265呎 (1房)
 $575万
 $21,715/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -28760,7 +28760,7 @@
           <t>P | 273呎 (1房)
 $527万
 $19,322/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -28768,7 +28768,7 @@
           <t>Q | 273呎 (1房)
 $522万
 $19,124/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -28783,7 +28783,7 @@
           <t>A | 512呎 (3房)
 $1129万
 $22,052/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -28791,7 +28791,7 @@
           <t>B | 397呎 (3房)
 $855万
 $21,546/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>C | 350呎 (2房)
 $746万
 $21,327/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>D | 350呎 (2房)
 $790万
 $22,564/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>E | 348呎 (2房)
 $746万
 $21,427/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>F | 348呎 (2房)
 $814万
 $23,397/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -28831,7 +28831,7 @@
           <t>G | 348呎 (2房)
 $850万
 $24,416/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -28839,7 +28839,7 @@
           <t>H | 348呎 (2房)
 $807万
 $23,183/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -28847,7 +28847,7 @@
           <t>J | 464呎 (3房)
 $1077万
 $23,214/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -28855,7 +28855,7 @@
           <t>K | 395呎 (3房)
 $882万
 $22,332/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -28863,7 +28863,7 @@
           <t>L | 270呎 (1房)
 $538万
 $19,932/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -28871,7 +28871,7 @@
           <t>M | 265呎 (1房)
 $508万
 $19,162/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -28887,7 +28887,7 @@
           <t>P | 273呎 (1房)
 $555万
 $20,336/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -28895,7 +28895,7 @@
           <t>Q | 273呎 (1房)
 $521万
 $19,068/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
           <t>A | 512呎 (3房)
 $1256万
 $24,537/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -28918,7 +28918,7 @@
           <t>B | 397呎 (3房)
 $850万
 $21,416/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -28926,7 +28926,7 @@
           <t>C | 350呎 (2房)
 $783万
 $22,379/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>D | 350呎 (2房)
 $744万
 $21,250/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -28942,7 +28942,7 @@
           <t>E | 348呎 (2房)
 $741万
 $21,300/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -28958,7 +28958,7 @@
           <t>G | 348呎 (2房)
 $800万
 $22,994/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -28966,7 +28966,7 @@
           <t>H | 348呎 (2房)
 $847万
 $24,326/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>K | 395呎 (3房)
 $872万
 $22,074/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -28990,7 +28990,7 @@
           <t>L | 270呎 (1房)
 $509万
 $18,863/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M18" s="23" t="inlineStr">
@@ -28998,7 +28998,7 @@
           <t>M | 265呎 (1房)
 $534万
 $20,169/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>P | 273呎 (1房)
 $553万
 $20,274/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="P18" s="23" t="inlineStr">
@@ -29022,7 +29022,7 @@
           <t>Q | 273呎 (1房)
 $519万
 $19,009/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
           <t>A | 512呎 (3房)
 $1183万
 $23,105/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>B | 397呎 (3房)
 $845万
 $21,287/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 350呎 (2房)
 $738万
 $21,075/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>D | 350呎 (2房)
 $739万
 $21,124/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>E | 348呎 (2房)
 $737万
 $21,173/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -29085,7 +29085,7 @@
           <t>G | 348呎 (2房)
 $795万
 $22,857/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>H | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -29109,7 +29109,7 @@
           <t>K | 395呎 (3房)
 $867万
 $21,942/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
@@ -29117,7 +29117,7 @@
           <t>L | 270呎 (1房)
 $536万
 $19,866/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M19" s="23" t="inlineStr">
@@ -29125,7 +29125,7 @@
           <t>M | 265呎 (1房)
 $503万
 $18,995/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -29141,7 +29141,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,095/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P19" s="23" t="inlineStr">
@@ -29149,7 +29149,7 @@
           <t>Q | 273呎 (1房)
 $545万
 $19,947/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
           <t>B | 397呎 (3房)
 $870万
 $21,906/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -29212,7 +29212,7 @@
           <t>G | 348呎 (2房)
 $795万
 $22,857/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -29220,7 +29220,7 @@
           <t>H | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -29236,7 +29236,7 @@
           <t>K | 395呎 (3房)
 $876万
 $22,186/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
@@ -29244,7 +29244,7 @@
           <t>L | 270呎 (1房)
 $508万
 $18,800/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M20" s="23" t="inlineStr">
@@ -29252,7 +29252,7 @@
           <t>M | 265呎 (1房)
 $503万
 $18,995/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -29268,7 +29268,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,095/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>Q | 273呎 (1房)
 $516万
 $18,897/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -29291,7 +29291,7 @@
           <t>A | 512呎 (3房)
 $1251万
 $24,437/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -29299,7 +29299,7 @@
           <t>B | 397呎 (3房)
 $896万
 $22,575/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -29307,7 +29307,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,695/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,747/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>E | 348呎 (2房)
 $793万
 $22,800/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -29339,7 +29339,7 @@
           <t>G | 348呎 (2房)
 $786万
 $22,583/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -29347,7 +29347,7 @@
           <t>H | 348呎 (2房)
 $788万
 $22,637/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -29363,7 +29363,7 @@
           <t>K | 395呎 (3房)
 $856万
 $21,675/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -29371,7 +29371,7 @@
           <t>L | 270呎 (1房)
 $568万
 $21,044/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="M21" s="23" t="inlineStr">
@@ -29379,7 +29379,7 @@
           <t>M | 265呎 (1房)
 $501万
 $18,917/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -29395,7 +29395,7 @@
           <t>P | 273呎 (1房)
 $518万
 $18,979/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="P21" s="23" t="inlineStr">
@@ -29403,7 +29403,7 @@
           <t>Q | 273呎 (1房)
 $514万
 $18,814/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -29413,12 +29413,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1309万
-$25,564/呎
-(在售)</t>
+$1178万
+$23,008/呎
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -29466,7 +29466,7 @@
           <t>G | 348呎 (2房)
 $794万
 $22,820/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -29474,7 +29474,7 @@
           <t>H | 348呎 (2房)
 $792万
 $22,750/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -29490,7 +29490,7 @@
           <t>K | 395呎 (3房)
 $924万
 $23,387/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -29498,7 +29498,7 @@
           <t>L | 270呎 (1房)
 $537万
 $19,877/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -29506,7 +29506,7 @@
           <t>M | 265呎 (1房)
 $535万
 $20,170/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -29522,7 +29522,7 @@
           <t>P | 273呎 (1房)
 $553万
 $20,268/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -29530,7 +29530,7 @@
           <t>Q | 273呎 (1房)
 $548万
 $20,057/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -29593,7 +29593,7 @@
           <t>G | 348呎 (2房)
 $767万
 $22,037/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -29601,7 +29601,7 @@
           <t>H | 348呎 (2房)
 $769万
 $22,089/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -29617,7 +29617,7 @@
           <t>K | 395呎 (3房)
 $809万
 $20,493/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L23" s="23" t="inlineStr">
@@ -29625,7 +29625,7 @@
           <t>L | 270呎 (1房)
 $562万
 $20,798/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="M23" s="23" t="inlineStr">
@@ -29633,7 +29633,7 @@
           <t>M | 265呎 (1房)
 $530万
 $19,990/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -29649,7 +29649,7 @@
           <t>P | 273呎 (1房)
 $579万
 $21,199/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="P23" s="23" t="inlineStr">
@@ -29657,7 +29657,7 @@
           <t>Q | 273呎 (1房)
 $573万
 $20,973/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
           <t>B | 397呎 (3房)
 $850万
 $21,401/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -29688,7 +29688,7 @@
           <t>C | 350呎 (2房)
 $691万
 $19,746/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -29696,7 +29696,7 @@
           <t>D | 350呎 (2房)
 $693万
 $19,795/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -29704,7 +29704,7 @@
           <t>E | 348呎 (2房)
 $690万
 $19,836/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -29720,7 +29720,7 @@
           <t>G | 348呎 (2房)
 $745万
 $21,422/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -29728,7 +29728,7 @@
           <t>H | 348呎 (2房)
 $760万
 $21,831/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -29744,7 +29744,7 @@
           <t>K | 395呎 (3房)
 $804万
 $20,365/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -29752,7 +29752,7 @@
           <t>L | 270呎 (1房)
 $566万
 $20,953/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M24" s="23" t="inlineStr">
@@ -29760,7 +29760,7 @@
           <t>M | 265呎 (1房)
 $528万
 $19,932/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -29776,7 +29776,7 @@
           <t>P | 273呎 (1房)
 $547万
 $20,021/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -29784,7 +29784,7 @@
           <t>Q | 273呎 (1房)
 $541万
 $19,810/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -29815,7 +29815,7 @@
           <t>C | 350呎 (2房)
 $684万
 $19,556/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -29823,7 +29823,7 @@
           <t>D | 350呎 (2房)
 $686万
 $19,605/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -29831,7 +29831,7 @@
           <t>E | 348呎 (2房)
 $684万
 $19,645/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -29839,7 +29839,7 @@
           <t>F | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -29871,7 +29871,7 @@
           <t>K | 395呎 (3房)
 $794万
 $20,110/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -29879,7 +29879,7 @@
           <t>L | 270呎 (1房)
 $529万
 $19,587/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M25" s="23" t="inlineStr">
@@ -29887,7 +29887,7 @@
           <t>M | 265呎 (1房)
 $527万
 $19,871/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -29903,7 +29903,7 @@
           <t>P | 273呎 (1房)
 $575万
 $21,067/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">
@@ -29911,7 +29911,7 @@
           <t>Q | 273呎 (1房)
 $539万
 $19,747/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -29942,7 +29942,7 @@
           <t>C | 350呎 (2房)
 $680万
 $19,430/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -29950,7 +29950,7 @@
           <t>D | 350呎 (2房)
 $682万
 $19,479/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -29958,7 +29958,7 @@
           <t>E | 348呎 (2房)
 $679万
 $19,518/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -29998,7 +29998,7 @@
           <t>K | 395呎 (3房)
 $779万
 $19,729/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -30006,7 +30006,7 @@
           <t>L | 270呎 (1房)
 $555万
 $20,566/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
@@ -30014,7 +30014,7 @@
           <t>M | 265呎 (1房)
 $553万
 $20,864/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -30030,7 +30030,7 @@
           <t>P | 273呎 (1房)
 $543万
 $19,899/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -30038,7 +30038,7 @@
           <t>Q | 273呎 (1房)
 $537万
 $19,685/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -30053,7 +30053,7 @@
           <t>A | 512呎 (3房)
 $1081万
 $21,117/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -30069,10 +30069,137 @@
           <t>C | 350呎 (2房)
 $713万
 $20,376/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$677万
+$19,353/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$712万
+$20,469/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$819万
+$23,532/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$739万
+$21,233/呎
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$741万
+$21,287/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$785万
+$19,864/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$548万
+$20,303/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="M27" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$546万
+$20,598/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O27" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$588万
+$21,537/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="P27" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$551万
+$20,186/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1201万
+$23,463/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$676万
+$19,304/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 350呎 (2房)
 $677万
@@ -30080,39 +30207,39 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 348呎 (2房)
-$712万
-$20,469/呎
-(26年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
+$675万
+$19,391/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$819万
-$23,532/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
+$737万
+$21,178/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>G | 348呎 (2房)
 $739万
 $21,233/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>H | 348呎 (2房)
-$741万
-$21,287/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
+$749万
+$21,524/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 464呎 (3房)
 -
@@ -30120,31 +30247,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>K | 395呎 (3房)
-$785万
-$19,864/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="L27" s="23" t="inlineStr">
+$772万
+$19,538/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>L | 270呎 (1房)
 $548万
 $20,303/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="M27" s="23" t="inlineStr">
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="M28" s="23" t="inlineStr">
         <is>
           <t>M | 265呎 (1房)
 $546万
 $20,598/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
         <is>
           <t>N | 349呎 (2房)
 -
@@ -30152,38 +30279,38 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O27" s="23" t="inlineStr">
+      <c r="O28" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
-$588万
-$21,537/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="P27" s="23" t="inlineStr">
+$557万
+$20,403/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="P28" s="23" t="inlineStr">
         <is>
           <t>Q | 273呎 (1房)
-$551万
-$20,186/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+$554万
+$20,298/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1201万
-$23,463/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
+$993万
+$19,392/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 397呎 (3房)
 -
@@ -30191,87 +30318,87 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-$676万
-$19,304/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
+$716万
+$20,471/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 350呎 (2房)
-$677万
-$19,353/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
+$718万
+$20,523/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 348呎 (2房)
-$675万
-$19,391/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
+$716万
+$20,563/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$737万
-$21,178/呎
-(26年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
+$727万
+$20,902/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>G | 348呎 (2房)
-$739万
-$21,233/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
+$729万
+$20,956/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>H | 348呎 (2房)
-$749万
-$21,524/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="inlineStr">
+$731万
+$21,010/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
         <is>
           <t>J | 464呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
+$928万
+$19,990/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>K | 395呎 (3房)
-$772万
-$19,538/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="L28" s="23" t="inlineStr">
+$761万
+$19,262/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>L | 270呎 (1房)
-$548万
-$20,303/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="M28" s="23" t="inlineStr">
+$545万
+$20,180/呎
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="M29" s="23" t="inlineStr">
         <is>
           <t>M | 265呎 (1房)
-$546万
-$20,598/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="N28" s="21" t="inlineStr">
+$543万
+$20,486/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
         <is>
           <t>N | 349呎 (2房)
 -
@@ -30279,126 +30406,126 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O28" s="23" t="inlineStr">
+      <c r="O29" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
-$557万
-$20,403/呎
+$554万
+$20,275/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$579万
+$21,220/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$983万
+$19,199/呎
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="P28" s="23" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$554万
-$20,298/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$993万
-$19,392/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 397呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
+$811万
+$20,435/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-$716万
-$20,471/呎
+$713万
+$20,378/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$751万
+$21,448/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$708万
+$20,359/呎
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$718万
-$20,523/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$716万
-$20,563/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$727万
-$20,902/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
+$760万
+$21,845/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>G | 348呎 (2房)
-$729万
-$20,956/呎
-(26年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="I29" s="23" t="inlineStr">
+$691万
+$19,866/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>H | 348呎 (2房)
-$731万
-$21,010/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
+$712万
+$20,455/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>J | 464呎 (3房)
-$928万
-$19,990/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
+$964万
+$20,777/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>K | 395呎 (3房)
-$761万
-$19,262/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="L29" s="23" t="inlineStr">
+$816万
+$20,661/呎
+(26年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
         <is>
           <t>L | 270呎 (1房)
-$545万
-$20,180/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="M29" s="23" t="inlineStr">
+$506万
+$18,743/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="M30" s="23" t="inlineStr">
         <is>
           <t>M | 265呎 (1房)
-$543万
-$20,486/呎
-(26年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
+$504万
+$19,015/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
         <is>
           <t>N | 349呎 (2房)
 -
@@ -30406,139 +30533,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O29" s="23" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$554万
-$20,275/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="P29" s="23" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$579万
-$21,220/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$983万
-$19,199/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$811万
-$20,435/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$713万
-$20,378/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$751万
-$21,448/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$708万
-$20,359/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$760万
-$21,845/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$691万
-$19,866/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$712万
-$20,455/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$964万
-$20,777/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$816万
-$20,661/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="L30" s="23" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$506万
-$18,743/呎
-(26年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$504万
-$19,015/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="N30" s="21" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
 $521万
 $19,091/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -30546,7 +30546,7 @@
           <t>Q | 273呎 (1房)
 $516万
 $18,884/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
           <t>A | 512呎 (3房)
 $1025万
 $20,017/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -30569,7 +30569,7 @@
           <t>B | 397呎 (3房)
 $790万
 $19,909/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -30577,7 +30577,7 @@
           <t>C | 350呎 (2房)
 $702万
 $20,056/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -30585,7 +30585,7 @@
           <t>D | 350呎 (2房)
 $704万
 $20,110/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -30593,7 +30593,7 @@
           <t>E | 348呎 (2房)
 $701万
 $20,147/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -30601,7 +30601,7 @@
           <t>F | 348呎 (2房)
 $703万
 $20,198/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -30609,7 +30609,7 @@
           <t>G | 348呎 (2房)
 $701万
 $20,130/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -30617,7 +30617,7 @@
           <t>H | 348呎 (2房)
 $702万
 $20,182/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -30625,7 +30625,7 @@
           <t>J | 464呎 (3房)
 $951万
 $20,503/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
@@ -30633,7 +30633,7 @@
           <t>K | 395呎 (3房)
 $796万
 $20,152/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -30641,7 +30641,7 @@
           <t>L | 270呎 (1房)
 $532万
 $19,721/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="M31" s="23" t="inlineStr">
@@ -30649,7 +30649,7 @@
           <t>M | 265呎 (1房)
 $531万
 $20,029/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -30657,7 +30657,7 @@
           <t>N | 349呎 (2房)
 $710万
 $20,358/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -30665,7 +30665,7 @@
           <t>P | 273呎 (1房)
 $548万
 $20,089/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr">
@@ -30673,7 +30673,7 @@
           <t>Q | 273呎 (1房)
 $542万
 $19,870/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -7057,23 +7057,23 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>10483000</v>
+        <v>9434700</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>26406</v>
+        <v>23765</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -18339,34 +18339,34 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>79010008612000</v>
+        <v>7750800</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>24606</v>
+        <v>22145</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>71109007750800</v>
+        <v>7750800</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>203168593574</v>
+        <v>22145</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28024,12 +28024,12 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 397呎 (3房)
-$1048万
-$26,406/呎
-(在售)</t>
+$943万
+$23,765/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -29556,12 +29556,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-$7901000861万
-$24,606/呎
-(在售)</t>
+$775万
+$22,145/呎
+(26年-08月-01日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -8698,7 +8698,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -28315,7 +28315,7 @@
           <t>F | 348呎 (2房)
 $833万
 $23,951/呎
-(26年-07月-20日)</t>
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -28442,7 +28442,7 @@
           <t>F | 348呎 (2房)
 $875万
 $25,137/呎
-(26年-07月-24日)</t>
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -14086,14 +14086,14 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
-        <v>8667000</v>
+        <v>9148500</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>21942</v>
+        <v>23161</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>8667000</v>
+        <v>9148500</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>21942</v>
+        <v>23161</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -29107,9 +29107,9 @@
       <c r="K19" s="23" t="inlineStr">
         <is>
           <t>K | 395呎 (3房)
-$867万
-$21,942/呎
-(26年-06月-11日)</t>
+$915万
+$23,161/呎
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -3901,23 +3901,23 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>9532000</v>
+        <v>8578800</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>27391</v>
+        <v>24652</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -6297,34 +6297,34 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>6742000</v>
+        <v>6404900</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>24696</v>
+        <v>23461</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>6067800</v>
+        <v>6404900</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>22226</v>
+        <v>23461</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -7243,23 +7243,23 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>6702000</v>
+        <v>6031800</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>24549</v>
+        <v>22095</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -8189,23 +8189,23 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>6683000</v>
+        <v>6014700</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>24480</v>
+        <v>22032</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="5" t="n">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="3" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -23257,23 +23257,23 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
-        <v>12013000</v>
+        <v>10811700</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>23463</v>
+        <v>21117</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K358" s="5" t="n">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N358" s="3" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27683,12 +27683,12 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>G | 348呎 (2房)
-$953万
-$27,391/呎
-(在售)</t>
+$858万
+$24,652/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -28120,12 +28120,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O11" s="20" t="inlineStr">
+      <c r="O11" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
-$674万
-$24,696/呎
-(在售)</t>
+$640万
+$23,461/呎
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -28247,12 +28247,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="O12" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
-$670万
-$24,549/呎
-(在售)</t>
+$603万
+$22,095/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="P12" s="23" t="inlineStr">
@@ -28374,12 +28374,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t>P | 273呎 (1房)
-$668万
-$24,480/呎
-(在售)</t>
+$601万
+$22,032/呎
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="P13" s="23" t="inlineStr">
@@ -29418,7 +29418,7 @@
           <t>A | 512呎 (3房)
 $1178万
 $23,008/呎
-(26年-07月-29日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -30175,12 +30175,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1201万
-$23,463/呎
-(在售)</t>
+$1081万
+$21,117/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -10445,34 +10445,34 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>9070000</v>
+        <v>8299000</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>26063</v>
+        <v>23848</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>8163000</v>
+        <v>8299000</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>23457</v>
+        <v>23848</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
@@ -18463,23 +18463,23 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
-        <v>12848000</v>
+        <v>11563200</v>
       </c>
       <c r="I283" s="5" t="n">
-        <v>25094</v>
+        <v>22584</v>
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K283" s="5" t="n">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
@@ -26413,38 +26413,30 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H408" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I408" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H408" s="5" t="n">
+        <v>11781000</v>
+      </c>
+      <c r="I408" s="5" t="n">
+        <v>33000</v>
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K408" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L408" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K408" s="5" t="n">
+        <v>11781000</v>
+      </c>
+      <c r="L408" s="5" t="n">
+        <v>33000</v>
       </c>
       <c r="M408" s="3" t="inlineStr">
         <is>
@@ -26453,7 +26445,7 @@
       </c>
       <c r="N408" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27170,7 +27162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27180,7 +27172,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28029,7 +28021,7 @@
           <t>B | 397呎 (3房)
 $943万
 $23,765/呎
-(26年-07月-30日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -28580,12 +28572,12 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>H | 348呎 (2房)
-$907万
-$26,063/呎
-(在售)</t>
+$830万
+$23,848/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -29540,12 +29532,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1285万
-$25,094/呎
-(在售)</t>
+$1156万
+$22,584/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -30755,12 +30747,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K32" s="20" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>K | 357呎 (3房)
-招标单位
--
-(在售)</t>
+$1178万
+$33,000/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -28498,7 +28498,7 @@
           <t>P | 273呎 (1房)
 $600万
 $21,963/呎
-(26年-07月-29日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="P14" s="23" t="inlineStr">
@@ -29553,7 +29553,7 @@
           <t>C | 350呎 (2房)
 $775万
 $22,145/呎
-(26年-08月-01日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -3009,23 +3009,23 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>9583000</v>
+        <v>8624700</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>27537</v>
+        <v>24784</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -18401,23 +18401,23 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
-        <v>9714000</v>
+        <v>8742600</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>24469</v>
+        <v>22022</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27540,12 +27540,12 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$958万
-$27,537/呎
-(在售)</t>
+$862万
+$24,784/呎
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -28117,7 +28117,7 @@
           <t>P | 273呎 (1房)
 $640万
 $23,461/呎
-(26年-08月-13日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -29540,12 +29540,12 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 397呎 (3房)
-$971万
-$24,469/呎
-(在售)</t>
+$874万
+$22,022/呎
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -2303,23 +2303,23 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>11298000</v>
+        <v>10168200</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>28458</v>
+        <v>25613</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27381,12 +27381,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 397呎 (3房)
-$1130万
-$28,458/呎
-(在售)</t>
+$1017万
+$25,613/呎
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -11507,23 +11507,23 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>9101000</v>
+        <v>8190900</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>26152</v>
+        <v>23537</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="5" t="n">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28371,7 +28371,7 @@
           <t>P | 273呎 (1房)
 $601万
 $22,032/呎
-(26年-08月-13日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="P13" s="23" t="inlineStr">
@@ -28683,12 +28683,12 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$910万
-$26,152/呎
-(在售)</t>
+$819万
+$23,537/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -26343,7 +26343,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -26353,12 +26353,12 @@
       </c>
       <c r="H407" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I407" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J407" s="3" t="inlineStr">
@@ -26368,12 +26368,12 @@
       </c>
       <c r="K407" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L407" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M407" s="3" t="inlineStr">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="N407" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26545,7 +26545,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -26555,12 +26555,12 @@
       </c>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J410" s="3" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M410" s="3" t="inlineStr">
@@ -26585,7 +26585,7 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -26625,12 +26625,12 @@
       </c>
       <c r="H411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J411" s="3" t="inlineStr">
@@ -26640,12 +26640,12 @@
       </c>
       <c r="K411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L411" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M411" s="3" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26685,7 +26685,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -26695,12 +26695,12 @@
       </c>
       <c r="H412" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I412" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J412" s="3" t="inlineStr">
@@ -26710,12 +26710,12 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M412" s="3" t="inlineStr">
@@ -26725,7 +26725,7 @@
       </c>
       <c r="N412" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26755,7 +26755,7 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -26765,12 +26765,12 @@
       </c>
       <c r="H413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J413" s="3" t="inlineStr">
@@ -26780,12 +26780,12 @@
       </c>
       <c r="K413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M413" s="3" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="N413" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -26835,12 +26835,12 @@
       </c>
       <c r="H414" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I414" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J414" s="3" t="inlineStr">
@@ -26850,12 +26850,12 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M414" s="3" t="inlineStr">
@@ -26865,7 +26865,7 @@
       </c>
       <c r="N414" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26895,7 +26895,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -26905,12 +26905,12 @@
       </c>
       <c r="H415" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I415" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J415" s="3" t="inlineStr">
@@ -26920,12 +26920,12 @@
       </c>
       <c r="K415" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L415" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M415" s="3" t="inlineStr">
@@ -26935,7 +26935,7 @@
       </c>
       <c r="N415" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -26975,12 +26975,12 @@
       </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J416" s="3" t="inlineStr">
@@ -26990,12 +26990,12 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M416" s="3" t="inlineStr">
@@ -27005,7 +27005,7 @@
       </c>
       <c r="N416" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -30683,60 +30683,60 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 359呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 312呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>C | 312呎 (2房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 312呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 311呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>D | 312呎 (2房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 311呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 311呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>E | 311呎 (2房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>H | 311呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>F | 311呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>G | 311呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>H | 311呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -30755,12 +30755,12 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="L32" s="21" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>L | 232呎 (1房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M32" s="20" t="inlineStr">
